--- a/preorder_forms/043_fitness_class_series_pre_order_form--preorder_forms.xlsx
+++ b/preorder_forms/043_fitness_class_series_pre_order_form--preorder_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fitness_class_series_preorder_form</t>
+          <t>title_and_first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>schedule_preferences</t>
+          <t>Title and First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>participant_1_first_name</t>
+          <t>title_and_last_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>Title and Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,64 +566,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_1_last_name</t>
+          <t>participant_1_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Participant 1's Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>participant_1_email</t>
+          <t>schedule_preferences_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Schedule Preferences 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>participant_2_first_name</t>
+          <t>schedule_preferences_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>Schedule Preferences 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,85 +635,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>participant_2_last_name</t>
+          <t>payment_details</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Payment Details</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_2_email</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>payment_details</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>payment_details</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>schedule_preferences</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>schedule_preferences</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -730,12 +684,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,51 +712,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>schedule_preferences_choices</t>
+          <t>schedule_preferences_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>schedule_preferences_choices</t>
+          <t>schedule_preferences_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>schedule_preferences_choices</t>
+          <t>schedule_preferences_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option_3'}</t>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>schedule_preferences_2_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>schedule_preferences_2_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>schedule_preferences_2_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
